--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.40209365430051</v>
+        <v>6.727840218823832</v>
       </c>
       <c r="D2" t="n">
-        <v>41.3513477625751</v>
+        <v>6.719594011418454</v>
       </c>
       <c r="E2" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F2" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.9292095397595</v>
+        <v>6.81349655021092</v>
       </c>
       <c r="D3" t="n">
-        <v>41.81383575484504</v>
+        <v>6.79474831016232</v>
       </c>
       <c r="E3" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F3" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.89788698734994</v>
+        <v>6.808406635444366</v>
       </c>
       <c r="D4" t="n">
-        <v>41.91268781314703</v>
+        <v>6.810811769636393</v>
       </c>
       <c r="E4" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F4" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.60198444132905</v>
+        <v>4.322822471715971</v>
       </c>
       <c r="D5" t="n">
-        <v>6.534873968010218</v>
+        <v>1.061917019801661</v>
       </c>
       <c r="E5" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F5" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.15023792196467</v>
+        <v>5.224413662319258</v>
       </c>
       <c r="D6" t="n">
-        <v>23.55421924930742</v>
+        <v>3.827560628012456</v>
       </c>
       <c r="E6" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F6" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.6381090374542</v>
+        <v>4.491192718586307</v>
       </c>
       <c r="D7" t="n">
-        <v>26.5070665630465</v>
+        <v>4.307398316495056</v>
       </c>
       <c r="E7" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F7" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.97559044145855</v>
+        <v>4.058533446737014</v>
       </c>
       <c r="D8" t="n">
-        <v>24.79478332876677</v>
+        <v>4.0291522909246</v>
       </c>
       <c r="E8" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F8" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.45509679908006</v>
+        <v>1.69895322985051</v>
       </c>
       <c r="D9" t="n">
-        <v>12.1772598509191</v>
+        <v>1.978804725774354</v>
       </c>
       <c r="E9" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F9" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>3.904188952055679</v>
+        <v>0.6344307047090478</v>
       </c>
       <c r="D10" t="n">
-        <v>3.865909416857505</v>
+        <v>0.6282102802393447</v>
       </c>
       <c r="E10" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F10" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.05214478198268</v>
+        <v>3.258473527072185</v>
       </c>
       <c r="D11" t="n">
-        <v>24.30221311541017</v>
+        <v>3.949109631254152</v>
       </c>
       <c r="E11" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F11" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.93328687583965</v>
+        <v>4.539159117323943</v>
       </c>
       <c r="D12" t="n">
-        <v>31.76310066380327</v>
+        <v>5.161503857868031</v>
       </c>
       <c r="E12" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F12" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>10.52241092964289</v>
+        <v>1.70989177606697</v>
       </c>
       <c r="D13" t="n">
-        <v>6.237311891202174</v>
+        <v>1.013563182320353</v>
       </c>
       <c r="E13" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F13" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.18491821668989</v>
+        <v>4.905049210212107</v>
       </c>
       <c r="D14" t="n">
-        <v>30.03838616177359</v>
+        <v>4.881237751288208</v>
       </c>
       <c r="E14" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F14" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.67879045589538</v>
+        <v>3.847803449083</v>
       </c>
       <c r="D15" t="n">
-        <v>21.50047208074584</v>
+        <v>3.493826713121198</v>
       </c>
       <c r="E15" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F15" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.66945237820626</v>
+        <v>2.546286011458518</v>
       </c>
       <c r="D16" t="n">
-        <v>6.650691895043788</v>
+        <v>1.080737432944616</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F16" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.41234480902449</v>
+        <v>4.454506031466479</v>
       </c>
       <c r="D17" t="n">
-        <v>27.03454960335008</v>
+        <v>4.393114310544388</v>
       </c>
       <c r="E17" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F17" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.79157996726441</v>
+        <v>3.378631744680467</v>
       </c>
       <c r="D18" t="n">
-        <v>20.62905712651606</v>
+        <v>3.352221783058859</v>
       </c>
       <c r="E18" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F18" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.18428552490027</v>
+        <v>6.692446397796294</v>
       </c>
       <c r="D19" t="n">
-        <v>31.79430517879164</v>
+        <v>5.166574591553642</v>
       </c>
       <c r="E19" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F19" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.36573406392448</v>
+        <v>7.696931785387727</v>
       </c>
       <c r="D20" t="n">
-        <v>47.0787551512469</v>
+        <v>7.650297712077621</v>
       </c>
       <c r="E20" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F20" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>23.01212576173459</v>
+        <v>3.73947043628187</v>
       </c>
       <c r="D21" t="n">
-        <v>23.36704277766669</v>
+        <v>3.797144451370837</v>
       </c>
       <c r="E21" t="n">
-        <v>11.47016971317001</v>
+        <v>1.863902578390126</v>
       </c>
       <c r="F21" t="n">
-        <v>12.49434241965855</v>
+        <v>2.030330643194515</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
